--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117572711</v>
+        <v>117572763</v>
       </c>
       <c r="B5" t="n">
         <v>97836</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490842</v>
+        <v>490841</v>
       </c>
       <c r="R5" t="n">
-        <v>6948544</v>
+        <v>6948543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117572763</v>
+        <v>117491664</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490841</v>
+        <v>490869</v>
       </c>
       <c r="R6" t="n">
-        <v>6948543</v>
+        <v>6948548</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117491664</v>
+        <v>117572711</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490869</v>
+        <v>490842</v>
       </c>
       <c r="R7" t="n">
-        <v>6948548</v>
+        <v>6948544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,22 +1362,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117492216</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117575343</v>
+        <v>117575821</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490840</v>
+        <v>490837</v>
       </c>
       <c r="R3" t="n">
-        <v>6948518</v>
+        <v>6948462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117575821</v>
+        <v>117575343</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490837</v>
+        <v>490840</v>
       </c>
       <c r="R4" t="n">
-        <v>6948462</v>
+        <v>6948518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117572763</v>
+        <v>117491664</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490841</v>
+        <v>490869</v>
       </c>
       <c r="R5" t="n">
-        <v>6948543</v>
+        <v>6948548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117491664</v>
+        <v>117572711</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490869</v>
+        <v>490842</v>
       </c>
       <c r="R6" t="n">
-        <v>6948548</v>
+        <v>6948544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117572711</v>
+        <v>117572763</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490842</v>
+        <v>490841</v>
       </c>
       <c r="R7" t="n">
-        <v>6948544</v>
+        <v>6948543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1413,7 +1413,7 @@
         <v>117975136</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -1536,10 +1536,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118245514</v>
+        <v>118246779</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,47 +1548,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågbacken (Sågbacken), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490773</v>
+        <v>490898</v>
       </c>
       <c r="R9" t="n">
-        <v>6948619</v>
+        <v>6948795</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1620,7 +1611,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1630,7 +1621,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,7 +1648,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118246779</v>
+        <v>118245632</v>
       </c>
       <c r="B10" t="n">
         <v>78484</v>
@@ -1697,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490898</v>
+        <v>490788</v>
       </c>
       <c r="R10" t="n">
-        <v>6948795</v>
+        <v>6948653</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118245632</v>
+        <v>118247282</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1809,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490788</v>
+        <v>490834</v>
       </c>
       <c r="R11" t="n">
-        <v>6948653</v>
+        <v>6948778</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1844,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118246537</v>
+        <v>118246844</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>79593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,47 +1889,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sågbacken (Sågbacken), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490877</v>
+        <v>490939</v>
       </c>
       <c r="R12" t="n">
-        <v>6948758</v>
+        <v>6948802</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1965,7 +1952,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118247282</v>
+        <v>118245514</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,38 +2001,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sågbacken (Sågbacken), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490834</v>
+        <v>490773</v>
       </c>
       <c r="R13" t="n">
-        <v>6948778</v>
+        <v>6948619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2077,7 +2073,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2083,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hällmark</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118246844</v>
+        <v>118246537</v>
       </c>
       <c r="B14" t="n">
-        <v>79593</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,38 +2122,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sågbacken (Sågbacken), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490939</v>
+        <v>490877</v>
       </c>
       <c r="R14" t="n">
-        <v>6948802</v>
+        <v>6948758</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2559,6 +2559,1929 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120088522</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490858</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6948582</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120092469</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490863</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6948889</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120089373</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6948604</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120091773</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490846</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6948822</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120087028</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490816</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6948520</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120087700</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490846</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6948551</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120092032</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490829</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6948828</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120091517</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490848</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6948795</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120087458</v>
+      </c>
+      <c r="B26" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490814</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6948533</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120090853</v>
+      </c>
+      <c r="B27" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490873</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6948716</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120086700</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6948476</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120090402</v>
+      </c>
+      <c r="B29" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490859</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6948716</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120091350</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>490848</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6948780</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120089959</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>490822</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6948664</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120091461</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490838</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6948784</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120088693</v>
+      </c>
+      <c r="B33" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>490846</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6948573</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120090399</v>
+      </c>
+      <c r="B34" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490859</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6948716</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088522</v>
+        <v>120092469</v>
       </c>
       <c r="B18" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490858</v>
+        <v>490863</v>
       </c>
       <c r="R18" t="n">
-        <v>6948582</v>
+        <v>6948889</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120092469</v>
+        <v>120088522</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490863</v>
+        <v>490858</v>
       </c>
       <c r="R19" t="n">
-        <v>6948889</v>
+        <v>6948582</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2753,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,12 +2763,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120091773</v>
+        <v>120087028</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,38 +2914,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490846</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6948822</v>
+        <v>6948520</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120087028</v>
+        <v>120091773</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,47 +3035,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490816</v>
+        <v>490846</v>
       </c>
       <c r="R22" t="n">
-        <v>6948520</v>
+        <v>6948822</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120054678</v>
+        <v>120054751</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490818</v>
+        <v>490817</v>
       </c>
       <c r="R16" t="n">
-        <v>6948499</v>
+        <v>6948537</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120054751</v>
+        <v>120054678</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490817</v>
+        <v>490818</v>
       </c>
       <c r="R17" t="n">
-        <v>6948537</v>
+        <v>6948499</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120092469</v>
+        <v>120090402</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490863</v>
+        <v>490859</v>
       </c>
       <c r="R18" t="n">
-        <v>6948889</v>
+        <v>6948716</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,12 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088522</v>
+        <v>120091461</v>
       </c>
       <c r="B19" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2718,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490858</v>
+        <v>490838</v>
       </c>
       <c r="R19" t="n">
-        <v>6948582</v>
+        <v>6948784</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2753,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089373</v>
+        <v>120092469</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490809</v>
+        <v>490863</v>
       </c>
       <c r="R20" t="n">
-        <v>6948604</v>
+        <v>6948889</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120087028</v>
+        <v>120090399</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,47 +2914,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490859</v>
       </c>
       <c r="R21" t="n">
-        <v>6948520</v>
+        <v>6948716</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2986,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091773</v>
+        <v>120090853</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,25 +3026,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490846</v>
+        <v>490873</v>
       </c>
       <c r="R22" t="n">
-        <v>6948822</v>
+        <v>6948716</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3098,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120087700</v>
+        <v>120087028</v>
       </c>
       <c r="B23" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,38 +3138,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490846</v>
+        <v>490816</v>
       </c>
       <c r="R23" t="n">
-        <v>6948551</v>
+        <v>6948520</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3359,10 +3359,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120091517</v>
+        <v>120088522</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>95455</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490848</v>
+        <v>490858</v>
       </c>
       <c r="R25" t="n">
-        <v>6948795</v>
+        <v>6948582</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3588,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120090853</v>
+        <v>120086700</v>
       </c>
       <c r="B27" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3604,21 +3604,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490873</v>
+        <v>490840</v>
       </c>
       <c r="R27" t="n">
-        <v>6948716</v>
+        <v>6948476</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,7 +3700,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086700</v>
+        <v>120089959</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490840</v>
+        <v>490822</v>
       </c>
       <c r="R28" t="n">
-        <v>6948476</v>
+        <v>6948664</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120090402</v>
+        <v>120091517</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>90562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,21 +3828,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490859</v>
+        <v>490848</v>
       </c>
       <c r="R29" t="n">
-        <v>6948716</v>
+        <v>6948795</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,10 +3924,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120091350</v>
+        <v>120091773</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>90527</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,25 +3936,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R30" t="n">
-        <v>6948780</v>
+        <v>6948822</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,10 +4036,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120089959</v>
+        <v>120088693</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490822</v>
+        <v>490846</v>
       </c>
       <c r="R31" t="n">
-        <v>6948664</v>
+        <v>6948573</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120091461</v>
+        <v>120091350</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490838</v>
+        <v>490848</v>
       </c>
       <c r="R32" t="n">
-        <v>6948784</v>
+        <v>6948780</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088693</v>
+        <v>120089373</v>
       </c>
       <c r="B33" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490846</v>
+        <v>490809</v>
       </c>
       <c r="R33" t="n">
-        <v>6948573</v>
+        <v>6948604</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120090399</v>
+        <v>120087700</v>
       </c>
       <c r="B34" t="n">
-        <v>82305</v>
+        <v>91494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490846</v>
       </c>
       <c r="R34" t="n">
-        <v>6948716</v>
+        <v>6948551</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -3247,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120092032</v>
+        <v>120087458</v>
       </c>
       <c r="B24" t="n">
-        <v>95455</v>
+        <v>82305</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490829</v>
+        <v>490814</v>
       </c>
       <c r="R24" t="n">
-        <v>6948828</v>
+        <v>6948533</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3332,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,7 +3364,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088522</v>
+        <v>120092032</v>
       </c>
       <c r="B25" t="n">
         <v>95455</v>
@@ -3399,10 +3404,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490858</v>
+        <v>490829</v>
       </c>
       <c r="R25" t="n">
-        <v>6948582</v>
+        <v>6948828</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3434,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3444,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,10 +3476,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120087458</v>
+        <v>120088522</v>
       </c>
       <c r="B26" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3492,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490814</v>
+        <v>490858</v>
       </c>
       <c r="R26" t="n">
-        <v>6948533</v>
+        <v>6948582</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3546,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3556,12 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090402</v>
+        <v>120090853</v>
       </c>
       <c r="B18" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490859</v>
+        <v>490873</v>
       </c>
       <c r="R18" t="n">
         <v>6948716</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120091461</v>
+        <v>120089959</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490838</v>
+        <v>490822</v>
       </c>
       <c r="R19" t="n">
-        <v>6948784</v>
+        <v>6948664</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,7 +2785,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120092469</v>
+        <v>120086700</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490863</v>
+        <v>490840</v>
       </c>
       <c r="R20" t="n">
-        <v>6948889</v>
+        <v>6948476</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,12 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,7 +2897,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090399</v>
+        <v>120087458</v>
       </c>
       <c r="B21" t="n">
         <v>82305</v>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490859</v>
+        <v>490814</v>
       </c>
       <c r="R21" t="n">
-        <v>6948716</v>
+        <v>6948533</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2982,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090853</v>
+        <v>120089373</v>
       </c>
       <c r="B22" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490873</v>
+        <v>490809</v>
       </c>
       <c r="R22" t="n">
-        <v>6948716</v>
+        <v>6948604</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120087028</v>
+        <v>120090402</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,47 +3138,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490816</v>
+        <v>490859</v>
       </c>
       <c r="R23" t="n">
-        <v>6948520</v>
+        <v>6948716</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3210,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120087458</v>
+        <v>120092469</v>
       </c>
       <c r="B24" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3263,21 +3254,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3287,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490814</v>
+        <v>490863</v>
       </c>
       <c r="R24" t="n">
-        <v>6948533</v>
+        <v>6948889</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,12 +3323,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3364,10 +3355,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120092032</v>
+        <v>120091517</v>
       </c>
       <c r="B25" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,21 +3371,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3404,10 +3395,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490829</v>
+        <v>490848</v>
       </c>
       <c r="R25" t="n">
-        <v>6948828</v>
+        <v>6948795</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3439,7 +3430,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3440,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3588,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086700</v>
+        <v>120091773</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3600,25 +3591,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3628,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490840</v>
+        <v>490846</v>
       </c>
       <c r="R27" t="n">
-        <v>6948476</v>
+        <v>6948822</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3663,7 +3654,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3673,7 +3664,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,10 +3691,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120089959</v>
+        <v>120091461</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3740,10 +3731,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490822</v>
+        <v>490838</v>
       </c>
       <c r="R28" t="n">
-        <v>6948664</v>
+        <v>6948784</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3775,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3785,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3812,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120091517</v>
+        <v>120088693</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,21 +3819,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3843,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R29" t="n">
-        <v>6948795</v>
+        <v>6948573</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3887,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120091773</v>
+        <v>120092032</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,25 +3927,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3964,10 +3955,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490846</v>
+        <v>490829</v>
       </c>
       <c r="R30" t="n">
-        <v>6948822</v>
+        <v>6948828</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3999,7 +3990,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +4000,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088693</v>
+        <v>120091350</v>
       </c>
       <c r="B31" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4052,21 +4043,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4076,10 +4067,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490846</v>
+        <v>490848</v>
       </c>
       <c r="R31" t="n">
-        <v>6948573</v>
+        <v>6948780</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4111,7 +4102,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4112,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4139,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120091350</v>
+        <v>120090399</v>
       </c>
       <c r="B32" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4155,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4179,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490848</v>
+        <v>490859</v>
       </c>
       <c r="R32" t="n">
-        <v>6948780</v>
+        <v>6948716</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4214,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4224,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4251,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120089373</v>
+        <v>120087700</v>
       </c>
       <c r="B33" t="n">
-        <v>95455</v>
+        <v>91494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4272,25 +4263,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4300,10 +4291,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490809</v>
+        <v>490846</v>
       </c>
       <c r="R33" t="n">
-        <v>6948604</v>
+        <v>6948551</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4335,7 +4326,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4345,7 +4336,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,10 +4363,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120087700</v>
+        <v>120087028</v>
       </c>
       <c r="B34" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,38 +4375,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490846</v>
+        <v>490816</v>
       </c>
       <c r="R34" t="n">
-        <v>6948551</v>
+        <v>6948520</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2897,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120087458</v>
+        <v>120089373</v>
       </c>
       <c r="B21" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490814</v>
+        <v>490809</v>
       </c>
       <c r="R21" t="n">
-        <v>6948533</v>
+        <v>6948604</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,12 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120089373</v>
+        <v>120087458</v>
       </c>
       <c r="B22" t="n">
-        <v>95455</v>
+        <v>82305</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,21 +3025,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490809</v>
+        <v>490814</v>
       </c>
       <c r="R22" t="n">
-        <v>6948604</v>
+        <v>6948533</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3089,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3094,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088522</v>
+        <v>120091773</v>
       </c>
       <c r="B26" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490858</v>
+        <v>490846</v>
       </c>
       <c r="R26" t="n">
-        <v>6948582</v>
+        <v>6948822</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120091773</v>
+        <v>120088522</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3591,25 +3591,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490846</v>
+        <v>490858</v>
       </c>
       <c r="R27" t="n">
-        <v>6948822</v>
+        <v>6948582</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120054751</v>
+        <v>120054678</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490817</v>
+        <v>490818</v>
       </c>
       <c r="R16" t="n">
-        <v>6948537</v>
+        <v>6948499</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120054678</v>
+        <v>120054751</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490818</v>
+        <v>490817</v>
       </c>
       <c r="R17" t="n">
-        <v>6948499</v>
+        <v>6948537</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090853</v>
+        <v>120087700</v>
       </c>
       <c r="B18" t="n">
-        <v>82305</v>
+        <v>91494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,25 +2573,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490873</v>
+        <v>490846</v>
       </c>
       <c r="R18" t="n">
-        <v>6948716</v>
+        <v>6948551</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120089959</v>
+        <v>120088693</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490822</v>
+        <v>490846</v>
       </c>
       <c r="R19" t="n">
-        <v>6948664</v>
+        <v>6948573</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120086700</v>
+        <v>120091773</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490840</v>
+        <v>490846</v>
       </c>
       <c r="R20" t="n">
-        <v>6948476</v>
+        <v>6948822</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120089373</v>
+        <v>120091517</v>
       </c>
       <c r="B21" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490809</v>
+        <v>490848</v>
       </c>
       <c r="R21" t="n">
-        <v>6948604</v>
+        <v>6948795</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120087458</v>
+        <v>120089373</v>
       </c>
       <c r="B22" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490814</v>
+        <v>490809</v>
       </c>
       <c r="R22" t="n">
-        <v>6948533</v>
+        <v>6948604</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090402</v>
+        <v>120090853</v>
       </c>
       <c r="B23" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,21 +3137,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,7 +3161,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490859</v>
+        <v>490873</v>
       </c>
       <c r="R23" t="n">
         <v>6948716</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120092469</v>
+        <v>120088522</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490863</v>
+        <v>490858</v>
       </c>
       <c r="R24" t="n">
-        <v>6948889</v>
+        <v>6948582</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3313,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,12 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120091517</v>
+        <v>120092469</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,21 +3361,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3395,10 +3385,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490848</v>
+        <v>490863</v>
       </c>
       <c r="R25" t="n">
-        <v>6948795</v>
+        <v>6948889</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3430,7 +3420,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,7 +3430,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120091773</v>
+        <v>120090399</v>
       </c>
       <c r="B26" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3479,25 +3474,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3507,10 +3502,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490846</v>
+        <v>490859</v>
       </c>
       <c r="R26" t="n">
-        <v>6948822</v>
+        <v>6948716</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3542,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3552,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088522</v>
+        <v>120090402</v>
       </c>
       <c r="B27" t="n">
-        <v>95455</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3590,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490858</v>
+        <v>490859</v>
       </c>
       <c r="R27" t="n">
-        <v>6948582</v>
+        <v>6948716</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3654,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3664,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3691,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120091461</v>
+        <v>120087458</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,21 +3702,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3731,10 +3726,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490838</v>
+        <v>490814</v>
       </c>
       <c r="R28" t="n">
-        <v>6948784</v>
+        <v>6948533</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3766,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3771,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088693</v>
+        <v>120089959</v>
       </c>
       <c r="B29" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490846</v>
+        <v>490822</v>
       </c>
       <c r="R29" t="n">
-        <v>6948573</v>
+        <v>6948664</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120092032</v>
+        <v>120086700</v>
       </c>
       <c r="B30" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490829</v>
+        <v>490840</v>
       </c>
       <c r="R30" t="n">
-        <v>6948828</v>
+        <v>6948476</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120091350</v>
+        <v>120087028</v>
       </c>
       <c r="B31" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,38 +4039,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490848</v>
+        <v>490816</v>
       </c>
       <c r="R31" t="n">
-        <v>6948780</v>
+        <v>6948520</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4102,7 +4111,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4112,7 +4121,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120090399</v>
+        <v>120091350</v>
       </c>
       <c r="B32" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4155,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4179,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490859</v>
+        <v>490848</v>
       </c>
       <c r="R32" t="n">
-        <v>6948716</v>
+        <v>6948780</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4214,7 +4223,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4224,7 +4233,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4251,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120087700</v>
+        <v>120092032</v>
       </c>
       <c r="B33" t="n">
-        <v>91494</v>
+        <v>95455</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4263,25 +4272,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4291,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490846</v>
+        <v>490829</v>
       </c>
       <c r="R33" t="n">
-        <v>6948551</v>
+        <v>6948828</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4326,7 +4335,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4336,7 +4345,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4363,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120087028</v>
+        <v>120091461</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4375,47 +4384,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490816</v>
+        <v>490838</v>
       </c>
       <c r="R34" t="n">
-        <v>6948520</v>
+        <v>6948784</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088693</v>
+        <v>120091517</v>
       </c>
       <c r="B19" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490846</v>
+        <v>490848</v>
       </c>
       <c r="R19" t="n">
-        <v>6948573</v>
+        <v>6948795</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120091773</v>
+        <v>120089373</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490846</v>
+        <v>490809</v>
       </c>
       <c r="R20" t="n">
-        <v>6948822</v>
+        <v>6948604</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120091517</v>
+        <v>120088693</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R21" t="n">
-        <v>6948795</v>
+        <v>6948573</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120089373</v>
+        <v>120091773</v>
       </c>
       <c r="B22" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490809</v>
+        <v>490846</v>
       </c>
       <c r="R22" t="n">
-        <v>6948604</v>
+        <v>6948822</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120091517</v>
+        <v>120088693</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R19" t="n">
-        <v>6948795</v>
+        <v>6948573</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089373</v>
+        <v>120091773</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490809</v>
+        <v>490846</v>
       </c>
       <c r="R20" t="n">
-        <v>6948604</v>
+        <v>6948822</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088693</v>
+        <v>120091517</v>
       </c>
       <c r="B21" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490846</v>
+        <v>490848</v>
       </c>
       <c r="R21" t="n">
-        <v>6948573</v>
+        <v>6948795</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091773</v>
+        <v>120089373</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,25 +3021,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490846</v>
+        <v>490809</v>
       </c>
       <c r="R22" t="n">
-        <v>6948822</v>
+        <v>6948604</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>120054678</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>120054751</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087700</v>
+        <v>120090853</v>
       </c>
       <c r="B18" t="n">
-        <v>91494</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,25 +2573,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490846</v>
+        <v>490873</v>
       </c>
       <c r="R18" t="n">
-        <v>6948551</v>
+        <v>6948716</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120091517</v>
+        <v>120087458</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490848</v>
+        <v>490814</v>
       </c>
       <c r="R19" t="n">
-        <v>6948795</v>
+        <v>6948533</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089373</v>
+        <v>120091461</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490809</v>
+        <v>490838</v>
       </c>
       <c r="R20" t="n">
-        <v>6948604</v>
+        <v>6948784</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088693</v>
+        <v>120086700</v>
       </c>
       <c r="B21" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490846</v>
+        <v>490840</v>
       </c>
       <c r="R21" t="n">
-        <v>6948573</v>
+        <v>6948476</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091773</v>
+        <v>120091350</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,25 +3026,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490846</v>
+        <v>490848</v>
       </c>
       <c r="R22" t="n">
-        <v>6948822</v>
+        <v>6948780</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090853</v>
+        <v>120089373</v>
       </c>
       <c r="B23" t="n">
-        <v>82305</v>
+        <v>95478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,21 +3142,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490873</v>
+        <v>490809</v>
       </c>
       <c r="R23" t="n">
-        <v>6948716</v>
+        <v>6948604</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3196,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088522</v>
+        <v>120087700</v>
       </c>
       <c r="B24" t="n">
-        <v>95455</v>
+        <v>91512</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3245,25 +3250,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490858</v>
+        <v>490846</v>
       </c>
       <c r="R24" t="n">
-        <v>6948582</v>
+        <v>6948551</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3308,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120092469</v>
+        <v>120088522</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>95478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,21 +3366,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,10 +3390,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490863</v>
+        <v>490858</v>
       </c>
       <c r="R25" t="n">
-        <v>6948889</v>
+        <v>6948582</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3420,7 +3425,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3430,12 +3435,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120090399</v>
+        <v>120088693</v>
       </c>
       <c r="B26" t="n">
-        <v>82305</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490859</v>
+        <v>490846</v>
       </c>
       <c r="R26" t="n">
-        <v>6948716</v>
+        <v>6948573</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120090402</v>
+        <v>120087028</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,38 +3586,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490859</v>
+        <v>490816</v>
       </c>
       <c r="R27" t="n">
-        <v>6948716</v>
+        <v>6948520</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3649,7 +3658,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3668,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3695,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087458</v>
+        <v>120091773</v>
       </c>
       <c r="B28" t="n">
-        <v>82305</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,25 +3707,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3726,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490814</v>
+        <v>490846</v>
       </c>
       <c r="R28" t="n">
-        <v>6948533</v>
+        <v>6948822</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3761,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,12 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3806,7 +3810,7 @@
         <v>120089959</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3915,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086700</v>
+        <v>120090402</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,21 +3935,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3955,10 +3959,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490840</v>
+        <v>490859</v>
       </c>
       <c r="R30" t="n">
-        <v>6948476</v>
+        <v>6948716</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3990,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4000,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4027,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120087028</v>
+        <v>120090399</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,47 +4043,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490816</v>
+        <v>490859</v>
       </c>
       <c r="R31" t="n">
-        <v>6948520</v>
+        <v>6948716</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4111,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120091350</v>
+        <v>120091517</v>
       </c>
       <c r="B32" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4159,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4191,7 +4186,7 @@
         <v>490848</v>
       </c>
       <c r="R32" t="n">
-        <v>6948780</v>
+        <v>6948795</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,7 +4258,7 @@
         <v>120092032</v>
       </c>
       <c r="B33" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4372,10 +4367,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120091461</v>
+        <v>120092469</v>
       </c>
       <c r="B34" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,21 +4383,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4412,10 +4407,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490838</v>
+        <v>490863</v>
       </c>
       <c r="R34" t="n">
-        <v>6948784</v>
+        <v>6948889</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4442,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4452,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2790,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120091461</v>
+        <v>120086700</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490838</v>
+        <v>490840</v>
       </c>
       <c r="R20" t="n">
-        <v>6948784</v>
+        <v>6948476</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120086700</v>
+        <v>120091461</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490840</v>
+        <v>490838</v>
       </c>
       <c r="R21" t="n">
-        <v>6948476</v>
+        <v>6948784</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3574,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120087028</v>
+        <v>120091773</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,47 +3586,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490816</v>
+        <v>490846</v>
       </c>
       <c r="R27" t="n">
-        <v>6948520</v>
+        <v>6948822</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3658,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3668,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3695,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120091773</v>
+        <v>120089959</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,25 +3698,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3735,10 +3726,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490846</v>
+        <v>490822</v>
       </c>
       <c r="R28" t="n">
-        <v>6948822</v>
+        <v>6948664</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3770,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120089959</v>
+        <v>120087028</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3819,38 +3810,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490822</v>
+        <v>490816</v>
       </c>
       <c r="R29" t="n">
-        <v>6948664</v>
+        <v>6948520</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120054678</v>
+        <v>120054751</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490818</v>
+        <v>490817</v>
       </c>
       <c r="R16" t="n">
-        <v>6948499</v>
+        <v>6948537</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120054751</v>
+        <v>120054678</v>
       </c>
       <c r="B17" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490817</v>
+        <v>490818</v>
       </c>
       <c r="R17" t="n">
-        <v>6948537</v>
+        <v>6948499</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090853</v>
+        <v>120087700</v>
       </c>
       <c r="B18" t="n">
-        <v>82321</v>
+        <v>91512</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,25 +2573,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490873</v>
+        <v>490846</v>
       </c>
       <c r="R18" t="n">
-        <v>6948716</v>
+        <v>6948551</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120087458</v>
+        <v>120090402</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490814</v>
+        <v>490859</v>
       </c>
       <c r="R19" t="n">
-        <v>6948533</v>
+        <v>6948716</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,12 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120086700</v>
+        <v>120090399</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490840</v>
+        <v>490859</v>
       </c>
       <c r="R20" t="n">
-        <v>6948476</v>
+        <v>6948716</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120091461</v>
+        <v>120086700</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490838</v>
+        <v>490840</v>
       </c>
       <c r="R21" t="n">
-        <v>6948784</v>
+        <v>6948476</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091350</v>
+        <v>120091773</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,25 +3021,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R22" t="n">
-        <v>6948780</v>
+        <v>6948822</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3089,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120089373</v>
+        <v>120091350</v>
       </c>
       <c r="B23" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,21 +3137,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490809</v>
+        <v>490848</v>
       </c>
       <c r="R23" t="n">
-        <v>6948604</v>
+        <v>6948780</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120087700</v>
+        <v>120092032</v>
       </c>
       <c r="B24" t="n">
-        <v>91512</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3250,25 +3245,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490846</v>
+        <v>490829</v>
       </c>
       <c r="R24" t="n">
-        <v>6948551</v>
+        <v>6948828</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3313,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088522</v>
+        <v>120090853</v>
       </c>
       <c r="B25" t="n">
-        <v>95478</v>
+        <v>82321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,21 +3361,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3390,10 +3385,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490858</v>
+        <v>490873</v>
       </c>
       <c r="R25" t="n">
-        <v>6948582</v>
+        <v>6948716</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3425,7 +3420,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3435,7 +3430,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088693</v>
+        <v>120089959</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,21 +3473,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3502,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490846</v>
+        <v>490822</v>
       </c>
       <c r="R26" t="n">
-        <v>6948573</v>
+        <v>6948664</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3537,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120091773</v>
+        <v>120088693</v>
       </c>
       <c r="B27" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,25 +3581,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,7 +3612,7 @@
         <v>490846</v>
       </c>
       <c r="R27" t="n">
-        <v>6948822</v>
+        <v>6948573</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3649,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120089959</v>
+        <v>120087028</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,38 +3693,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490822</v>
+        <v>490816</v>
       </c>
       <c r="R28" t="n">
-        <v>6948664</v>
+        <v>6948520</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3761,7 +3765,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3775,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120087028</v>
+        <v>120087458</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,47 +3814,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490816</v>
+        <v>490814</v>
       </c>
       <c r="R29" t="n">
-        <v>6948520</v>
+        <v>6948533</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3882,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3887,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120090402</v>
+        <v>120088522</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>95478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,21 +3935,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490859</v>
+        <v>490858</v>
       </c>
       <c r="R30" t="n">
-        <v>6948716</v>
+        <v>6948582</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120090399</v>
+        <v>120091461</v>
       </c>
       <c r="B31" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490859</v>
+        <v>490838</v>
       </c>
       <c r="R31" t="n">
-        <v>6948716</v>
+        <v>6948784</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120091517</v>
+        <v>120089373</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,21 +4159,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490848</v>
+        <v>490809</v>
       </c>
       <c r="R32" t="n">
-        <v>6948795</v>
+        <v>6948604</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120092032</v>
+        <v>120091517</v>
       </c>
       <c r="B33" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490829</v>
+        <v>490848</v>
       </c>
       <c r="R33" t="n">
-        <v>6948828</v>
+        <v>6948795</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -3121,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120091350</v>
+        <v>120092032</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>95478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490848</v>
+        <v>490829</v>
       </c>
       <c r="R23" t="n">
-        <v>6948780</v>
+        <v>6948828</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120092032</v>
+        <v>120091350</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490829</v>
+        <v>490848</v>
       </c>
       <c r="R24" t="n">
-        <v>6948828</v>
+        <v>6948780</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120089959</v>
+        <v>120088693</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490822</v>
+        <v>490846</v>
       </c>
       <c r="R26" t="n">
-        <v>6948664</v>
+        <v>6948573</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088693</v>
+        <v>120089959</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490846</v>
+        <v>490822</v>
       </c>
       <c r="R27" t="n">
-        <v>6948573</v>
+        <v>6948664</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087700</v>
+        <v>120090399</v>
       </c>
       <c r="B18" t="n">
-        <v>91512</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,25 +2573,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490846</v>
+        <v>490859</v>
       </c>
       <c r="R18" t="n">
-        <v>6948551</v>
+        <v>6948716</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090402</v>
+        <v>120087458</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490859</v>
+        <v>490814</v>
       </c>
       <c r="R19" t="n">
-        <v>6948716</v>
+        <v>6948533</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,7 +2790,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090399</v>
+        <v>120088693</v>
       </c>
       <c r="B20" t="n">
         <v>82321</v>
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490859</v>
+        <v>490846</v>
       </c>
       <c r="R20" t="n">
-        <v>6948716</v>
+        <v>6948573</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120086700</v>
+        <v>120091517</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490840</v>
+        <v>490848</v>
       </c>
       <c r="R21" t="n">
-        <v>6948476</v>
+        <v>6948795</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091773</v>
+        <v>120087028</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,38 +3026,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490846</v>
+        <v>490816</v>
       </c>
       <c r="R22" t="n">
-        <v>6948822</v>
+        <v>6948520</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3098,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3108,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,7 +3135,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120092032</v>
+        <v>120088522</v>
       </c>
       <c r="B23" t="n">
         <v>95478</v>
@@ -3161,10 +3175,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490829</v>
+        <v>490858</v>
       </c>
       <c r="R23" t="n">
-        <v>6948828</v>
+        <v>6948582</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3196,7 +3210,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3220,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120091350</v>
+        <v>120086700</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,21 +3263,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490848</v>
+        <v>490840</v>
       </c>
       <c r="R24" t="n">
-        <v>6948780</v>
+        <v>6948476</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3308,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3332,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3359,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120090853</v>
+        <v>120091773</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,25 +3371,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490873</v>
+        <v>490846</v>
       </c>
       <c r="R25" t="n">
-        <v>6948716</v>
+        <v>6948822</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3420,7 +3434,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3430,7 +3444,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3457,7 +3471,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088693</v>
+        <v>120090853</v>
       </c>
       <c r="B26" t="n">
         <v>82321</v>
@@ -3497,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490846</v>
+        <v>490873</v>
       </c>
       <c r="R26" t="n">
-        <v>6948573</v>
+        <v>6948716</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3532,7 +3546,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3556,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,7 +3583,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120089959</v>
+        <v>120092469</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3609,10 +3623,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490822</v>
+        <v>490863</v>
       </c>
       <c r="R27" t="n">
-        <v>6948664</v>
+        <v>6948889</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3644,7 +3658,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3668,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3700,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087028</v>
+        <v>120087700</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,47 +3712,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490816</v>
+        <v>490846</v>
       </c>
       <c r="R28" t="n">
-        <v>6948520</v>
+        <v>6948551</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3765,7 +3775,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3775,7 +3785,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3802,10 +3812,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120087458</v>
+        <v>120089373</v>
       </c>
       <c r="B29" t="n">
-        <v>82321</v>
+        <v>95478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3818,21 +3828,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3842,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490814</v>
+        <v>490809</v>
       </c>
       <c r="R29" t="n">
-        <v>6948533</v>
+        <v>6948604</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3877,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3887,12 +3897,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3924,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088522</v>
+        <v>120091461</v>
       </c>
       <c r="B30" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,21 +3940,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3959,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490858</v>
+        <v>490838</v>
       </c>
       <c r="R30" t="n">
-        <v>6948582</v>
+        <v>6948784</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3994,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,10 +4036,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120091461</v>
+        <v>120089959</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4047,21 +4052,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490838</v>
+        <v>490822</v>
       </c>
       <c r="R31" t="n">
-        <v>6948784</v>
+        <v>6948664</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4106,7 +4111,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4121,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120089373</v>
+        <v>120091350</v>
       </c>
       <c r="B32" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4183,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490809</v>
+        <v>490848</v>
       </c>
       <c r="R32" t="n">
-        <v>6948604</v>
+        <v>6948780</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4233,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120091517</v>
+        <v>120092032</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490848</v>
+        <v>490829</v>
       </c>
       <c r="R33" t="n">
-        <v>6948795</v>
+        <v>6948828</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4330,7 +4335,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4340,7 +4345,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4367,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120092469</v>
+        <v>120090402</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4383,21 +4388,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4407,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490863</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>6948889</v>
+        <v>6948716</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4442,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4452,12 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120054751</v>
+        <v>120054678</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490817</v>
+        <v>490818</v>
       </c>
       <c r="R16" t="n">
-        <v>6948537</v>
+        <v>6948499</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120054678</v>
+        <v>120054751</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490818</v>
+        <v>490817</v>
       </c>
       <c r="R17" t="n">
-        <v>6948499</v>
+        <v>6948537</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3247,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120086700</v>
+        <v>120091773</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3259,25 +3259,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490840</v>
+        <v>490846</v>
       </c>
       <c r="R24" t="n">
-        <v>6948476</v>
+        <v>6948822</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,10 +3359,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120091773</v>
+        <v>120086700</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,25 +3371,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490846</v>
+        <v>490840</v>
       </c>
       <c r="R25" t="n">
-        <v>6948822</v>
+        <v>6948476</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120089373</v>
+        <v>120091461</v>
       </c>
       <c r="B29" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,21 +3828,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490809</v>
+        <v>490838</v>
       </c>
       <c r="R29" t="n">
-        <v>6948604</v>
+        <v>6948784</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,10 +3924,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120091461</v>
+        <v>120089373</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490838</v>
+        <v>490809</v>
       </c>
       <c r="R30" t="n">
-        <v>6948784</v>
+        <v>6948604</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2561,7 +2561,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090399</v>
+        <v>120090853</v>
       </c>
       <c r="B18" t="n">
         <v>82321</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490859</v>
+        <v>490873</v>
       </c>
       <c r="R18" t="n">
         <v>6948716</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120087458</v>
+        <v>120089373</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>95478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490814</v>
+        <v>490809</v>
       </c>
       <c r="R19" t="n">
-        <v>6948533</v>
+        <v>6948604</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,12 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088693</v>
+        <v>120091517</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490846</v>
+        <v>490848</v>
       </c>
       <c r="R20" t="n">
-        <v>6948573</v>
+        <v>6948795</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120091517</v>
+        <v>120087458</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490848</v>
+        <v>490814</v>
       </c>
       <c r="R21" t="n">
-        <v>6948795</v>
+        <v>6948533</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2982,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120087028</v>
+        <v>120090402</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,47 +3026,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490816</v>
+        <v>490859</v>
       </c>
       <c r="R22" t="n">
-        <v>6948520</v>
+        <v>6948716</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3098,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088522</v>
+        <v>120090399</v>
       </c>
       <c r="B23" t="n">
-        <v>95478</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,21 +3142,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3175,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490858</v>
+        <v>490859</v>
       </c>
       <c r="R23" t="n">
-        <v>6948582</v>
+        <v>6948716</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3210,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120091773</v>
+        <v>120088693</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3259,25 +3250,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3290,7 +3281,7 @@
         <v>490846</v>
       </c>
       <c r="R24" t="n">
-        <v>6948822</v>
+        <v>6948573</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120086700</v>
+        <v>120088522</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,21 +3366,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3399,10 +3390,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490840</v>
+        <v>490858</v>
       </c>
       <c r="R25" t="n">
-        <v>6948476</v>
+        <v>6948582</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3434,7 +3425,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3444,7 +3435,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120090853</v>
+        <v>120091773</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,25 +3474,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3502,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490873</v>
+        <v>490846</v>
       </c>
       <c r="R26" t="n">
-        <v>6948716</v>
+        <v>6948822</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3546,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3556,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,7 +3574,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120092469</v>
+        <v>120089959</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3623,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490863</v>
+        <v>490822</v>
       </c>
       <c r="R27" t="n">
-        <v>6948889</v>
+        <v>6948664</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3658,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3668,12 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087700</v>
+        <v>120086700</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3712,25 +3698,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3740,10 +3726,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490846</v>
+        <v>490840</v>
       </c>
       <c r="R28" t="n">
-        <v>6948551</v>
+        <v>6948476</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3775,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3785,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3924,10 +3910,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120089373</v>
+        <v>120087028</v>
       </c>
       <c r="B30" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,38 +3922,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490809</v>
+        <v>490816</v>
       </c>
       <c r="R30" t="n">
-        <v>6948604</v>
+        <v>6948520</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3999,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,7 +4031,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120089959</v>
+        <v>120092469</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490822</v>
+        <v>490863</v>
       </c>
       <c r="R31" t="n">
-        <v>6948664</v>
+        <v>6948889</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4111,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4116,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120091350</v>
+        <v>120087700</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490848</v>
+        <v>490846</v>
       </c>
       <c r="R32" t="n">
-        <v>6948780</v>
+        <v>6948551</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4372,7 +4372,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120090402</v>
+        <v>120091350</v>
       </c>
       <c r="B34" t="n">
         <v>74654</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490859</v>
+        <v>490848</v>
       </c>
       <c r="R34" t="n">
-        <v>6948716</v>
+        <v>6948780</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120054678</v>
+        <v>120054751</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490818</v>
+        <v>490817</v>
       </c>
       <c r="R16" t="n">
-        <v>6948499</v>
+        <v>6948537</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120054751</v>
+        <v>120054678</v>
       </c>
       <c r="B17" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490817</v>
+        <v>490818</v>
       </c>
       <c r="R17" t="n">
-        <v>6948537</v>
+        <v>6948499</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090853</v>
+        <v>120086700</v>
       </c>
       <c r="B18" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490873</v>
+        <v>490840</v>
       </c>
       <c r="R18" t="n">
-        <v>6948716</v>
+        <v>6948476</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,7 +2673,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120089373</v>
+        <v>120092032</v>
       </c>
       <c r="B19" t="n">
         <v>95478</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490809</v>
+        <v>490829</v>
       </c>
       <c r="R19" t="n">
-        <v>6948604</v>
+        <v>6948828</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120091517</v>
+        <v>120087458</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490848</v>
+        <v>490814</v>
       </c>
       <c r="R20" t="n">
-        <v>6948795</v>
+        <v>6948533</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2870,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120087458</v>
+        <v>120091461</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490814</v>
+        <v>490838</v>
       </c>
       <c r="R21" t="n">
-        <v>6948533</v>
+        <v>6948784</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,12 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090402</v>
+        <v>120090853</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490859</v>
+        <v>490873</v>
       </c>
       <c r="R22" t="n">
         <v>6948716</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090399</v>
+        <v>120091773</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,25 +3138,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490859</v>
+        <v>490846</v>
       </c>
       <c r="R23" t="n">
-        <v>6948716</v>
+        <v>6948822</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088693</v>
+        <v>120087028</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3250,38 +3250,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490846</v>
+        <v>490816</v>
       </c>
       <c r="R24" t="n">
-        <v>6948573</v>
+        <v>6948520</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3313,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3332,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3359,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088522</v>
+        <v>120091517</v>
       </c>
       <c r="B25" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,21 +3375,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3390,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490858</v>
+        <v>490848</v>
       </c>
       <c r="R25" t="n">
-        <v>6948582</v>
+        <v>6948795</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3425,7 +3434,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3435,7 +3444,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120091773</v>
+        <v>120090399</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3483,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3502,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490846</v>
+        <v>490859</v>
       </c>
       <c r="R26" t="n">
-        <v>6948822</v>
+        <v>6948716</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3537,7 +3546,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3556,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,10 +3583,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120089959</v>
+        <v>120089373</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,21 +3599,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3614,10 +3623,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490822</v>
+        <v>490809</v>
       </c>
       <c r="R27" t="n">
-        <v>6948664</v>
+        <v>6948604</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3649,7 +3658,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3668,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,7 +3695,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086700</v>
+        <v>120089959</v>
       </c>
       <c r="B28" t="n">
         <v>78542</v>
@@ -3726,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490840</v>
+        <v>490822</v>
       </c>
       <c r="R28" t="n">
-        <v>6948476</v>
+        <v>6948664</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3761,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120091461</v>
+        <v>120088693</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3814,21 +3823,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3838,10 +3847,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490838</v>
+        <v>490846</v>
       </c>
       <c r="R29" t="n">
-        <v>6948784</v>
+        <v>6948573</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3873,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120087028</v>
+        <v>120091350</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3922,47 +3931,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490816</v>
+        <v>490848</v>
       </c>
       <c r="R30" t="n">
-        <v>6948520</v>
+        <v>6948780</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120092469</v>
+        <v>120087700</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,25 +4043,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490863</v>
+        <v>490846</v>
       </c>
       <c r="R31" t="n">
-        <v>6948889</v>
+        <v>6948551</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,12 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120087700</v>
+        <v>120088522</v>
       </c>
       <c r="B32" t="n">
-        <v>91512</v>
+        <v>95478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,25 +4155,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490846</v>
+        <v>490858</v>
       </c>
       <c r="R32" t="n">
-        <v>6948551</v>
+        <v>6948582</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120092032</v>
+        <v>120090402</v>
       </c>
       <c r="B33" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,21 +4271,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4300,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490829</v>
+        <v>490859</v>
       </c>
       <c r="R33" t="n">
-        <v>6948828</v>
+        <v>6948716</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4335,7 +4330,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4345,7 +4340,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,10 +4367,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120091350</v>
+        <v>120092469</v>
       </c>
       <c r="B34" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,21 +4383,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4412,10 +4407,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490848</v>
+        <v>490863</v>
       </c>
       <c r="R34" t="n">
-        <v>6948780</v>
+        <v>6948889</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4442,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4452,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2902,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120091461</v>
+        <v>120087028</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,38 +2914,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490838</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6948784</v>
+        <v>6948520</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2977,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090853</v>
+        <v>120091461</v>
       </c>
       <c r="B22" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,21 +3039,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490873</v>
+        <v>490838</v>
       </c>
       <c r="R22" t="n">
-        <v>6948716</v>
+        <v>6948784</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3089,7 +3098,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3108,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120091773</v>
+        <v>120090853</v>
       </c>
       <c r="B23" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,25 +3147,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3175,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490846</v>
+        <v>490873</v>
       </c>
       <c r="R23" t="n">
-        <v>6948822</v>
+        <v>6948716</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3201,7 +3210,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3220,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120087028</v>
+        <v>120091773</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3250,47 +3259,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490816</v>
+        <v>490846</v>
       </c>
       <c r="R24" t="n">
-        <v>6948520</v>
+        <v>6948822</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120086700</v>
+        <v>120088693</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490840</v>
+        <v>490846</v>
       </c>
       <c r="R18" t="n">
-        <v>6948476</v>
+        <v>6948573</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120092032</v>
+        <v>120091773</v>
       </c>
       <c r="B19" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490829</v>
+        <v>490846</v>
       </c>
       <c r="R19" t="n">
-        <v>6948828</v>
+        <v>6948822</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120087458</v>
+        <v>120091350</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490814</v>
+        <v>490848</v>
       </c>
       <c r="R20" t="n">
-        <v>6948533</v>
+        <v>6948780</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,12 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med gamla granar där arten kan leva</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120087028</v>
+        <v>120090399</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,47 +2909,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490859</v>
       </c>
       <c r="R21" t="n">
-        <v>6948520</v>
+        <v>6948716</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2986,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091461</v>
+        <v>120092469</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,21 +3025,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490838</v>
+        <v>490863</v>
       </c>
       <c r="R22" t="n">
-        <v>6948784</v>
+        <v>6948889</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3098,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,7 +3094,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090853</v>
+        <v>120087700</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>91512</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,25 +3138,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3175,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490873</v>
+        <v>490846</v>
       </c>
       <c r="R23" t="n">
-        <v>6948716</v>
+        <v>6948551</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3210,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120091773</v>
+        <v>120092032</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3259,25 +3250,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3287,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490846</v>
+        <v>490829</v>
       </c>
       <c r="R24" t="n">
-        <v>6948822</v>
+        <v>6948828</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3322,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120091517</v>
+        <v>120088522</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,21 +3366,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3399,10 +3390,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490848</v>
+        <v>490858</v>
       </c>
       <c r="R25" t="n">
-        <v>6948795</v>
+        <v>6948582</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3434,7 +3425,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3444,7 +3435,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120090399</v>
+        <v>120091517</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3478,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3502,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490859</v>
+        <v>490848</v>
       </c>
       <c r="R26" t="n">
-        <v>6948716</v>
+        <v>6948795</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3546,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3556,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120089373</v>
+        <v>120091461</v>
       </c>
       <c r="B27" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,21 +3590,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3623,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490809</v>
+        <v>490838</v>
       </c>
       <c r="R27" t="n">
-        <v>6948604</v>
+        <v>6948784</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3658,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3668,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3695,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120089959</v>
+        <v>120087028</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,38 +3698,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490822</v>
+        <v>490816</v>
       </c>
       <c r="R28" t="n">
-        <v>6948664</v>
+        <v>6948520</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088693</v>
+        <v>120089959</v>
       </c>
       <c r="B29" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490846</v>
+        <v>490822</v>
       </c>
       <c r="R29" t="n">
-        <v>6948573</v>
+        <v>6948664</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120091350</v>
+        <v>120087458</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,21 +3935,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490848</v>
+        <v>490814</v>
       </c>
       <c r="R30" t="n">
-        <v>6948780</v>
+        <v>6948533</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4004,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med gamla granar där arten kan leva</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,10 +4036,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120087700</v>
+        <v>120090853</v>
       </c>
       <c r="B31" t="n">
-        <v>91512</v>
+        <v>82321</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,25 +4048,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490846</v>
+        <v>490873</v>
       </c>
       <c r="R31" t="n">
-        <v>6948551</v>
+        <v>6948716</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4106,7 +4111,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4121,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088522</v>
+        <v>120090402</v>
       </c>
       <c r="B32" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4183,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490858</v>
+        <v>490859</v>
       </c>
       <c r="R32" t="n">
-        <v>6948582</v>
+        <v>6948716</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4233,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120090402</v>
+        <v>120086700</v>
       </c>
       <c r="B33" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490859</v>
+        <v>490840</v>
       </c>
       <c r="R33" t="n">
-        <v>6948716</v>
+        <v>6948476</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4330,7 +4335,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4340,7 +4345,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4367,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120092469</v>
+        <v>120089373</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4383,21 +4388,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4407,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490863</v>
+        <v>490809</v>
       </c>
       <c r="R34" t="n">
-        <v>6948889</v>
+        <v>6948604</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4442,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4452,12 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -2785,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120091350</v>
+        <v>120090853</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490848</v>
+        <v>490873</v>
       </c>
       <c r="R20" t="n">
-        <v>6948780</v>
+        <v>6948716</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090399</v>
+        <v>120087028</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2909,38 +2909,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490859</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6948716</v>
+        <v>6948520</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2972,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2991,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120092469</v>
+        <v>120091350</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,21 +3034,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +3058,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490863</v>
+        <v>490848</v>
       </c>
       <c r="R22" t="n">
-        <v>6948889</v>
+        <v>6948780</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3084,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3103,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3130,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120087700</v>
+        <v>120090399</v>
       </c>
       <c r="B23" t="n">
-        <v>91512</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,25 +3142,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3170,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490846</v>
+        <v>490859</v>
       </c>
       <c r="R23" t="n">
-        <v>6948551</v>
+        <v>6948716</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3201,7 +3205,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3215,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120092032</v>
+        <v>120089959</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,21 +3258,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3282,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490829</v>
+        <v>490822</v>
       </c>
       <c r="R24" t="n">
-        <v>6948828</v>
+        <v>6948664</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3313,7 +3317,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3327,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088522</v>
+        <v>120091461</v>
       </c>
       <c r="B25" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,21 +3370,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3390,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490858</v>
+        <v>490838</v>
       </c>
       <c r="R25" t="n">
-        <v>6948582</v>
+        <v>6948784</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3425,7 +3429,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3435,7 +3439,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3574,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120091461</v>
+        <v>120092032</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,21 +3594,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3614,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490838</v>
+        <v>490829</v>
       </c>
       <c r="R27" t="n">
-        <v>6948784</v>
+        <v>6948828</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3663,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3690,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087028</v>
+        <v>120087700</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,47 +3702,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490816</v>
+        <v>490846</v>
       </c>
       <c r="R28" t="n">
-        <v>6948520</v>
+        <v>6948551</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3770,7 +3765,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3775,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120089959</v>
+        <v>120088522</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,21 +3818,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3847,10 +3842,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490822</v>
+        <v>490858</v>
       </c>
       <c r="R29" t="n">
-        <v>6948664</v>
+        <v>6948582</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3882,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3887,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4036,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120090853</v>
+        <v>120086700</v>
       </c>
       <c r="B31" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4052,21 +4047,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490873</v>
+        <v>490840</v>
       </c>
       <c r="R31" t="n">
-        <v>6948716</v>
+        <v>6948476</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4111,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120090402</v>
+        <v>120092469</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4159,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490859</v>
+        <v>490863</v>
       </c>
       <c r="R32" t="n">
-        <v>6948716</v>
+        <v>6948889</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4233,7 +4228,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086700</v>
+        <v>120089373</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490840</v>
+        <v>490809</v>
       </c>
       <c r="R33" t="n">
-        <v>6948476</v>
+        <v>6948604</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120089373</v>
+        <v>120090402</v>
       </c>
       <c r="B34" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490809</v>
+        <v>490859</v>
       </c>
       <c r="R34" t="n">
-        <v>6948604</v>
+        <v>6948716</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -3018,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120091350</v>
+        <v>120090399</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490848</v>
+        <v>490859</v>
       </c>
       <c r="R22" t="n">
-        <v>6948780</v>
+        <v>6948716</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090399</v>
+        <v>120089959</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490859</v>
+        <v>490822</v>
       </c>
       <c r="R23" t="n">
-        <v>6948716</v>
+        <v>6948664</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120089959</v>
+        <v>120091350</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490822</v>
+        <v>490848</v>
       </c>
       <c r="R24" t="n">
-        <v>6948664</v>
+        <v>6948780</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4604,7 +4604,7 @@
         <v>125881837</v>
       </c>
       <c r="B36" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4821,6 +4821,341 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126027763</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>490929</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6948728</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126027266</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98332</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490871</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6948713</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126028083</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490922</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6948745</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126027266</v>
       </c>
       <c r="B39" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4936,54 +4936,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126027266</v>
+        <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>91228</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490871</v>
+        <v>490922</v>
       </c>
       <c r="R39" t="n">
-        <v>6948713</v>
+        <v>6948745</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5015,7 +5006,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5025,7 +5016,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,45 +5043,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126028083</v>
+        <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490922</v>
+        <v>490871</v>
       </c>
       <c r="R40" t="n">
-        <v>6948745</v>
+        <v>6948713</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4604,7 +4604,7 @@
         <v>125881837</v>
       </c>
       <c r="B36" t="n">
-        <v>79054</v>
+        <v>79058</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>125881837</v>
       </c>
       <c r="B36" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>126027763</v>
       </c>
       <c r="B38" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4936,45 +4936,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126028083</v>
+        <v>126027266</v>
       </c>
       <c r="B39" t="n">
-        <v>91236</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490922</v>
+        <v>490871</v>
       </c>
       <c r="R39" t="n">
-        <v>6948745</v>
+        <v>6948713</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5006,7 +5015,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5016,7 +5025,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5043,54 +5052,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126027266</v>
+        <v>126028083</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>91238</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490871</v>
+        <v>490922</v>
       </c>
       <c r="R40" t="n">
-        <v>6948713</v>
+        <v>6948745</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4936,54 +4936,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126027266</v>
+        <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>91238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490871</v>
+        <v>490922</v>
       </c>
       <c r="R39" t="n">
-        <v>6948713</v>
+        <v>6948745</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5015,7 +5006,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5025,7 +5016,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,45 +5043,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126028083</v>
+        <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>91238</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490922</v>
+        <v>490871</v>
       </c>
       <c r="R40" t="n">
-        <v>6948745</v>
+        <v>6948713</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>125881837</v>
       </c>
       <c r="B36" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>126027763</v>
       </c>
       <c r="B38" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5157,337 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126423293</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490920</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6948710</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126423367</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490928</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6948733</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126423167</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>490899</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6948691</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>125881837</v>
       </c>
       <c r="B36" t="n">
-        <v>79063</v>
+        <v>79066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125882354</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>126027763</v>
       </c>
       <c r="B38" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>126423293</v>
       </c>
       <c r="B41" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>126423367</v>
       </c>
       <c r="B42" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>126423167</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4936,45 +4936,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126028083</v>
+        <v>126027266</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490922</v>
+        <v>490871</v>
       </c>
       <c r="R39" t="n">
-        <v>6948745</v>
+        <v>6948713</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5006,7 +5015,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5016,7 +5025,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5043,54 +5052,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126027266</v>
+        <v>126028083</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490871</v>
+        <v>490922</v>
       </c>
       <c r="R40" t="n">
-        <v>6948713</v>
+        <v>6948745</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5488,6 +5488,872 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126617761</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490796</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6948815</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126618110</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490834</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6948751</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126617266</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490886</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6948756</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126616802</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>490870</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6948578</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126617665</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490846</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6948814</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>22:16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>22:16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126618195</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490834</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6948751</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126617695</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>490829</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6948820</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126617481</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490860</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6948810</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4936,54 +4936,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126027266</v>
+        <v>126028083</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490871</v>
+        <v>490922</v>
       </c>
       <c r="R39" t="n">
-        <v>6948713</v>
+        <v>6948745</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5015,7 +5006,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5025,7 +5016,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,45 +5043,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126028083</v>
+        <v>126027266</v>
       </c>
       <c r="B40" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490922</v>
+        <v>490871</v>
       </c>
       <c r="R40" t="n">
-        <v>6948745</v>
+        <v>6948713</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -5493,7 +5493,7 @@
         <v>126617761</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>126618110</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126617266</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>126617665</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>126617695</v>
       </c>
       <c r="B50" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>126617481</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>126882175</v>
       </c>
       <c r="B52" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>126883576</v>
       </c>
       <c r="B57" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>126883590</v>
       </c>
       <c r="B59" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -5493,7 +5493,7 @@
         <v>126617761</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>126618110</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126617266</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>126617665</v>
       </c>
       <c r="B48" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>126617695</v>
       </c>
       <c r="B50" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>126617481</v>
       </c>
       <c r="B51" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>126882175</v>
       </c>
       <c r="B52" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>126883576</v>
       </c>
       <c r="B57" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>126883590</v>
       </c>
       <c r="B59" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -6359,7 +6359,7 @@
         <v>126882175</v>
       </c>
       <c r="B52" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7348,6 +7348,225 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127459061</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>490759</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6948610</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127457982</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490813</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6948567</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -6359,7 +6359,7 @@
         <v>126882175</v>
       </c>
       <c r="B52" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>126883092</v>
       </c>
       <c r="B55" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>126883576</v>
       </c>
       <c r="B57" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>126882597</v>
       </c>
       <c r="B58" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>126883590</v>
       </c>
       <c r="B59" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>126943364</v>
       </c>
       <c r="B60" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>127457982</v>
       </c>
       <c r="B62" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -6359,7 +6359,7 @@
         <v>126882175</v>
       </c>
       <c r="B52" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126883816</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>126882900</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>126882341</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>126883576</v>
       </c>
       <c r="B57" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>126883590</v>
       </c>
       <c r="B59" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>126943364</v>
       </c>
       <c r="B60" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>127457982</v>
       </c>
       <c r="B62" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7567,6 +7567,113 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127839214</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>490875</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6948656</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>127457982</v>
       </c>
       <c r="B62" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127839214</v>
       </c>
       <c r="B63" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>127457982</v>
       </c>
       <c r="B62" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127839214</v>
       </c>
       <c r="B63" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>127459061</v>
       </c>
       <c r="B61" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -7572,7 +7572,7 @@
         <v>127839214</v>
       </c>
       <c r="B63" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>56876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,6 +4513,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>hane</t>
@@ -4523,6 +4524,7 @@
           <t>stationär</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
@@ -4575,6 +4577,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>23:05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Observerad ett flertal gånger under sommaren 2025</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7572,7 +7579,7 @@
         <v>127839214</v>
       </c>
       <c r="B63" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29383-2023 artfynd.xlsx
+++ b/artfynd/A 29383-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>125862430</v>
       </c>
       <c r="B35" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
